--- a/docs/modelos_importacao/10_Exemplo_Tabela_Referencia_TESTE.xlsx
+++ b/docs/modelos_importacao/10_Exemplo_Tabela_Referencia_TESTE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabela de referência'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tabela de referência'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leia-me'!$A$1:$B$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -464,31 +464,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BENGUELA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HUAMBO</t>
+          <t>BENGUELA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HUÍLA</t>
+          <t>BIÉ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="6">
@@ -504,15 +504,135 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>CUANDO CUBANGO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CUANZA NORTE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CUANZA SUL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CUNENE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HUAMBO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HUÍLA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LUNDA NORTE</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LUNDA SUL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MALANJE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>MOXICO</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B16" t="n">
         <v>1.15</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NAMIBE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UÍGE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ZAIRE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B7"/>
+  <autoFilter ref="A1:B19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -550,7 +670,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tabela fictícia para testar a importação.</t>
+          <t>Fator regional fictício para as 18 províncias.</t>
         </is>
       </c>
     </row>
